--- a/thermal_analysis_results.xlsx
+++ b/thermal_analysis_results.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.823300376042875</v>
+        <v>6.042220282132013</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.914145938586551</v>
+        <v>8.133065844675688</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.29989017338739</v>
+        <v>16.51881007947652</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.30607547201138</v>
+        <v>32.40731481492841</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.39692103455505</v>
+        <v>34.49816037747208</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.78266526935589</v>
+        <v>42.88390461227291</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54.30188259989397</v>
+        <v>58.403121942811</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56.39272816243765</v>
+        <v>60.49396750535468</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64.77847239723849</v>
+        <v>68.87971174015551</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.823300376042877</v>
+        <v>6.042220282132011</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.91414593858655</v>
+        <v>8.133065844675688</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.29989017338739</v>
+        <v>16.51881007947652</v>
       </c>
     </row>
     <row r="14">
@@ -823,13 +823,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97B57266-7696-4C01-8045-B7C2015C6C7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EC6E5D-D429-49F6-B22A-879562D58739}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59E5EB18-D663-4BFC-BBD7-412AB9F84165}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0A0546F-1FE4-4490-A674-E6DC1C73EF58}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CED783E8-B4D4-40EC-AEF1-314F60C00797}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0985BD66-2A75-47F3-BF83-D72C343EFF2F}"/>
 </file>
--- a/thermal_analysis_results.xlsx
+++ b/thermal_analysis_results.xlsx
@@ -823,13 +823,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EC6E5D-D429-49F6-B22A-879562D58739}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A2D3A-5244-4384-B988-B2BCCACE6774}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0A0546F-1FE4-4490-A674-E6DC1C73EF58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A311D359-4F0B-42F2-9DE6-DBEA74FBBC12}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0985BD66-2A75-47F3-BF83-D72C343EFF2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73501B2-1DF7-40E6-A215-ED214B312CE5}"/>
 </file>
--- a/thermal_analysis_results.xlsx
+++ b/thermal_analysis_results.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.042220282132013</v>
+        <v>11.1698609718881</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.133065844675688</v>
+        <v>13.30091510294224</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.51881007947652</v>
+        <v>16.50604330807044</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.40731481492841</v>
+        <v>37.92109778288587</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>34.49816037747208</v>
+        <v>40.05215191394</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.88390461227291</v>
+        <v>43.25728011906821</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58.403121942811</v>
+        <v>64.41682427861237</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60.49396750535468</v>
+        <v>66.5478784096665</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68.87971174015551</v>
+        <v>69.75300661479471</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.042220282132011</v>
+        <v>11.16986097188811</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.133065844675688</v>
+        <v>13.30091510294223</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.51881007947652</v>
+        <v>16.50604330807045</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25.9958071278826</v>
+        <v>26.49572649572649</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25.9958071278826</v>
+        <v>26.49572649572649</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.9958071278826</v>
+        <v>26.4957264957265</v>
       </c>
     </row>
   </sheetData>
@@ -823,13 +823,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89A2D3A-5244-4384-B988-B2BCCACE6774}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DEBF10C-4D18-4D1D-A449-56AAE07B45DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A311D359-4F0B-42F2-9DE6-DBEA74FBBC12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A68AEAEA-376B-43E0-8FB7-7FCAA4D9CC8C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B73501B2-1DF7-40E6-A215-ED214B312CE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96BDDF06-B535-49B8-AB2D-371F08570C66}"/>
 </file>
--- a/thermal_analysis_results.xlsx
+++ b/thermal_analysis_results.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.1698609718881</v>
+        <v>2.676638176638177</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.30091510294224</v>
+        <v>4.807692307692307</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.50604330807044</v>
+        <v>9.081196581196579</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.92109778288587</v>
+        <v>19.42787498763595</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.05215191394</v>
+        <v>21.55892911869007</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43.25728011906821</v>
+        <v>25.83243339219435</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64.41682427861237</v>
+        <v>45.92360148336244</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.5478784096665</v>
+        <v>48.05465561441657</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.75300661479471</v>
+        <v>52.32815988792084</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.16986097188811</v>
+        <v>2.676638176638178</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.30091510294223</v>
+        <v>4.807692307692307</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.50604330807045</v>
+        <v>9.081196581196579</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.4957264957265</v>
+        <v>26.49572649572649</v>
       </c>
     </row>
   </sheetData>
@@ -596,8 +596,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7113F119DDDD94DABB6595D7D00AF56" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0f7a63f121b558f8b37cc344fde8b2d7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="55d53729-a723-4cf0-8bd4-072a35a42187" xmlns:ns3="58762c00-8721-4b19-9291-0f1f7f71a825" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="14e8d373e99a6b4250baa42f02cf19bf" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7113F119DDDD94DABB6595D7D00AF56" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="967769522ba303b0ec80e9a3c77c671d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="55d53729-a723-4cf0-8bd4-072a35a42187" xmlns:ns3="58762c00-8721-4b19-9291-0f1f7f71a825" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d7627f20a84b56bc539a76fa2096f1c" ns2:_="" ns3:_="">
     <xsd:import namespace="55d53729-a723-4cf0-8bd4-072a35a42187"/>
     <xsd:import namespace="58762c00-8721-4b19-9291-0f1f7f71a825"/>
     <xsd:element name="properties">
@@ -823,13 +823,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DEBF10C-4D18-4D1D-A449-56AAE07B45DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0106306B-E202-44A2-99ED-7F8235488FD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A68AEAEA-376B-43E0-8FB7-7FCAA4D9CC8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE0A14E6-2E8C-42A0-B7C4-B34761124618}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96BDDF06-B535-49B8-AB2D-371F08570C66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDB75A41-5D50-4E97-8E9E-9E52E945E16F}"/>
 </file>
--- a/thermal_analysis_results.xlsx
+++ b/thermal_analysis_results.xlsx
@@ -823,13 +823,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0106306B-E202-44A2-99ED-7F8235488FD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{745992C0-C8BC-4ADF-8E92-49478D5B5D14}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE0A14E6-2E8C-42A0-B7C4-B34761124618}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32E9C922-C115-44D2-8340-B2E7C3AF936E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDB75A41-5D50-4E97-8E9E-9E52E945E16F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFE4053-1748-4EA3-9D3A-C342726029D4}"/>
 </file>